--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:44:30+00:00</t>
+          <t>2026-08-17T06:56:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:56:43+00:00</t>
+          <t>2026-08-17T07:44:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:44:10+00:00</t>
+          <t>2026-08-17T08:01:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:01:46+00:00</t>
+          <t>2026-08-17T08:15:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:15:12+00:00</t>
+          <t>2026-08-17T08:30:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:30:28+00:00</t>
+          <t>2026-08-17T09:22:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:22:46+00:00</t>
+          <t>2026-08-17T09:28:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:28:11+00:00</t>
+          <t>2026-08-17T10:46:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T10:46:52+00:00</t>
+          <t>2026-08-17T12:53:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:53:20+00:00</t>
+          <t>2026-08-17T23:15:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T23:15:51+00:00</t>
+          <t>2026-08-18T05:54:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:54:22+00:00</t>
+          <t>2026-08-18T23:16:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T23:16:03+00:00</t>
+          <t>2026-08-19T23:16:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:16:43+00:00</t>
+          <t>2026-08-20T23:19:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20T23:19:18+00:00</t>
+          <t>2026-08-21T23:16:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21T23:16:48+00:00</t>
+          <t>2026-08-22T23:14:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22T23:14:40+00:00</t>
+          <t>2026-08-23T23:14:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23T23:14:11+00:00</t>
+          <t>2026-08-24T23:17:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:17:17+00:00</t>
+          <t>2026-08-25T23:19:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:19:07+00:00</t>
+          <t>2026-08-27T04:11:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27T04:11:16+00:00</t>
+          <t>2026-08-28T06:27:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:27:47+00:00</t>
+          <t>2026-08-29T04:00:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29T04:00:05+00:00</t>
+          <t>2026-08-30T00:57:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30T00:57:40+00:00</t>
+          <t>2026-08-31T01:02:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31T01:02:17+00:00</t>
+          <t>2026-09-01T01:32:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01T01:32:47+00:00</t>
+          <t>2026-09-02T00:42:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:42:43+00:00</t>
+          <t>2026-09-03T00:54:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03T00:54:35+00:00</t>
+          <t>2026-09-04T00:34:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04T00:34:55+00:00</t>
+          <t>2026-09-05T00:32:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T00:32:21+00:00</t>
+          <t>2026-09-06T00:25:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06T00:25:14+00:00</t>
+          <t>2026-09-07T00:32:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T00:32:28+00:00</t>
+          <t>2026-09-07T07:50:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T07:50:48+00:00</t>
+          <t>2026-09-07T09:44:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:44:19+00:00</t>
+          <t>2026-09-07T11:03:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:03:57+00:00</t>
+          <t>2026-09-08T00:51:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:51:21+00:00</t>
+          <t>2026-09-09T00:55:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T00:55:09+00:00</t>
+          <t>2026-09-09T01:46:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:46:39+00:00</t>
+          <t>2026-09-09T02:39:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T02:39:36+00:00</t>
+          <t>2026-09-10T00:45:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10T00:45:15+00:00</t>
+          <t>2026-09-11T00:43:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11T00:43:36+00:00</t>
+          <t>2026-09-12T00:51:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12T00:51:37+00:00</t>
+          <t>2026-09-13T00:32:12+00:00</t>
         </is>
       </c>
     </row>
